--- a/r5-core-50-Gemeindekennziffer/StructureDefinition-at-core-ext-valueset-systemoid.xlsx
+++ b/r5-core-50-Gemeindekennziffer/StructureDefinition-at-core-ext-valueset-systemoid.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-ext-valueset-systemoid</t>
+    <t>https://fhir.hl7.at/core/r5/StructureDefinition/at-core-ext-valueset-systemoid</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-07T12:16:57+00:00</t>
+    <t>2026-10-13T08:41:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -139,10 +139,10 @@
     <t>element:ValueSet.expansion.contains</t>
   </si>
   <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-valueset#ValueSet.compose.include</t>
-  </si>
-  <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-valueset#ValueSet.expansion.contains</t>
+    <t>element:https://fhir.hl7.at/core/r5/StructureDefinition/at-core-valueset#ValueSet.compose.include</t>
+  </si>
+  <si>
+    <t>element:https://fhir.hl7.at/core/r5/StructureDefinition/at-core-valueset#ValueSet.expansion.contains</t>
   </si>
   <si>
     <t>ID</t>
